--- a/Smaers_etal_2011_b/Smaers_etal_2011_b_registry_rows.xlsx
+++ b/Smaers_etal_2011_b/Smaers_etal_2011_b_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R92c45edca2ae46ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rd3e16ca5f5b547ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Re20f90f4ef5a4d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rd2943c72f17a4be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Ra52c091140144f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R9ad0f58b25994534"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Cortical and cerebellar regional volumes</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Table 2: Volumetric data from earlier studies, new delineations and unpublished records</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — anatomy overlap review; not play extraction
@@ -350,13 +350,13 @@
         <x:v>Francesca Hicks dissertation: Table 1 note, Behavioural Data and References (local final draft). Smaers_etal_2018_Figure2-data1.README.md and existing volume inputs.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 11 / printed p. 186. Volumes in mm³; retain individual collection numbers and source-column groups. Includes Smaers 2010 and Stephan records; check existing volume lineage before adding any value.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/0220071004/Smaers-2011-Modeling the evolution of cortico-.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -514,7 +514,9 @@
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table 2</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Fran: cited as play source; papers concern anatomy. Planned folder: Smaers_etal_2011_b. Target: Source tables / results to select. Distinct publication from the existing Smaers_etal_2011 (10.1159/000323671). Suffix _b preserves that folder. Verify raw data, collection lineage and overlap; not a play-data source.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote correction 2026-10-25: Verified in EndNote full text — PDF p. 11 / printed p. 186. Volumes in mm³; retain individual collection numbers and source-column groups. Includes Smaers 2010 and Stephan records; check existing volume lineage before adding any value. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/0220071004/Smaers-2011-Modeling the evolution of cortico-.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — anatomy overlap review; not play extraction</x:v>
@@ -562,7 +564,9 @@
       </x:c>
       <x:c r="AC2" s="3"/>
       <x:c r="AD2" s="3"/>
-      <x:c r="AE2" s="3"/>
+      <x:c r="AE2" s="3" t="str">
+        <x:v>both</x:v>
+      </x:c>
       <x:c r="AF2" s="3"/>
       <x:c r="AG2" s="3" t="str">
         <x:v>These are anatomical sources, not independent play datasets. Compare with existing Smaers 2010/2011/2018 and volume-merge lineage first. Distinct DOI alone does not establish new measurements. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
@@ -701,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>Blank Item number means full text is still required or the source is REFERENCE ONLY. The six EndNote PDFs identified on 2026-10-25 are linked in Source list and their source-folder notes. Smaers 2013 Table 1 is now verified. Human snapshot checks remain pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -985,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B28B6D7-5013-442D-9047-BEB11A380500}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BFCCFD6-B38A-4CF6-8869-11A1996E64CD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0486F2-6036-46E1-A299-EA0D9C00441E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FA3EA6-1B60-41D4-8BAA-74675C1C2131}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17BA52C-1362-4383-A16B-7976605D3BE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF8FF36-E0A5-416C-90D2-8B0C1F563CD2}"/>
 </file>